--- a/artfynd/A 43619-2024 artfynd.xlsx
+++ b/artfynd/A 43619-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>61973417</v>
       </c>
       <c r="B2" t="n">
-        <v>95247</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97812</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494094.0586913634</v>
+        <v>494094</v>
       </c>
       <c r="R2" t="n">
-        <v>6518781.904360999</v>
+        <v>6518782</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2016-07-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-07-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61973412</v>
+        <v>61973418</v>
       </c>
       <c r="B3" t="n">
-        <v>77756</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,23 +783,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6459</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Barkkornlav</t>
-        </is>
+        <v>6455</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
+          <t>Scytinium lichenoides s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -827,10 +798,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494094.0586913634</v>
+        <v>494094</v>
       </c>
       <c r="R3" t="n">
-        <v>6518781.904360999</v>
+        <v>6518782</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,21 +831,11 @@
           <t>2016-07-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-07-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -883,11 +844,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>lind</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -904,15 +860,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61973413</v>
+        <v>61973412</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +871,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>6459</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +895,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494094.0586913634</v>
+        <v>494094</v>
       </c>
       <c r="R4" t="n">
-        <v>6518781.904360999</v>
+        <v>6518782</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,21 +928,11 @@
           <t>2016-07-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-07-09</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1000,6 +941,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>lind</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,15 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61973418</v>
+        <v>61973413</v>
       </c>
       <c r="B5" t="n">
-        <v>78449</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,14 +973,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6455</v>
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides s. lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1047,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494094.0586913634</v>
+        <v>494094</v>
       </c>
       <c r="R5" t="n">
-        <v>6518781.904360999</v>
+        <v>6518782</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1080,19 +1030,9 @@
           <t>2016-07-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-07-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,12 +1062,7 @@
         <v>61973414</v>
       </c>
       <c r="B6" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,10 +1094,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494094.0586913634</v>
+        <v>494094</v>
       </c>
       <c r="R6" t="n">
-        <v>6518781.904360999</v>
+        <v>6518782</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1192,19 +1127,9 @@
           <t>2016-07-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-07-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
